--- a/StructureDefinition-mii-pr-mikrobio-molekulare-pathogenlast.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-molekulare-pathogenlast.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T16:03:21+00:00</t>
+    <t>2026-09-10T13:00:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2121,7 +2121,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-probe)
 </t>
   </si>
   <si>

--- a/StructureDefinition-mii-pr-mikrobio-molekulare-pathogenlast.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-molekulare-pathogenlast.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:00:57+00:00</t>
+    <t>2026-09-10T16:03:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-molekulare-pathogenlast.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-molekulare-pathogenlast.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:03:25+00:00</t>
+    <t>2026-09-10T16:53:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-molekulare-pathogenlast.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-molekulare-pathogenlast.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:53:22+00:00</t>
+    <t>2026-09-10T17:52:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-molekulare-pathogenlast.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-molekulare-pathogenlast.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:52:15+00:00</t>
+    <t>2026-09-11T12:05:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-molekulare-pathogenlast.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-molekulare-pathogenlast.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:05:40+00:00</t>
+    <t>2026-09-12T16:32:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-molekulare-pathogenlast.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-molekulare-pathogenlast.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T16:32:25+00:00</t>
+    <t>2026-09-12T17:28:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-molekulare-pathogenlast.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-molekulare-pathogenlast.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T17:28:38+00:00</t>
+    <t>2026-09-12T20:31:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
